--- a/app/pipeline_output/akmeee/mapping_akmeee_COMBINED.xlsx
+++ b/app/pipeline_output/akmeee/mapping_akmeee_COMBINED.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -565,7 +565,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -643,47 +643,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>LeadStage</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>LOANPARAMETER1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanParameters.1.value</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'LeadStage' → 'LOANPARAMETER0' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Describes the status of the loan application process.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -714,16 +714,16 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BranchName' → 'LOANPARAMETER0' (frequency=12)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Identifies the processing branch for the loan, which is an application-level attribute.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -759,16 +759,16 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DealerName' → 'LOANPARAMETER122' (frequency=12)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Identifies the dealer associated with the asset being financed, a loan-level detail.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -778,227 +778,227 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SalesPointName</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>LOANPARAMETER4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanParameters.4.value</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SalesPointName' → 'LOANPARAMETER2' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Refers to the point of sale for the loan application, an operational parameter.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>ReferredBy</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>LOANPARAMETER5</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanParameters.5.value</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'ReferredBy' → 'LOANPARAMETER3' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F8" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Represents the referral source or channel for the loan application rather than a personal reference.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SubProduct</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>LOANPARAMETER6</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanParameters.6.value</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SubProduct' → 'LOANPARAMETER43' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Specifies the loan product variant, a core loan attribute.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SubProductCategory</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>LOANPARAMETER7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanParameters.7.value</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SubProductCategory' → 'LOANPARAMETER44' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Specifies the category of the loan product, a core loan attribute.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CreateDate</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>LOANPARAMETER8</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanParameters.8.value</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'CreateDate' → 'LOANPARAMETER116' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Represents the creation timestamp of the loan application itself.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1048,47 +1048,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>RegisterThrough</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>LOANPARAMETER9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanParameters.9.value</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'RegisterThrough' → 'LOANPARAMETER125' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Describes the channel used for loan registration, an application-level property.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1380,25 +1380,25 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>LOANPARAMETER10</t>
+          <t>LOANAPPLICANTPARAM1</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.10.value</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.0.value</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'Age' → 'LOANPARAMETER1' (frequency=6)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Represents the age of the applicant, a core demographic detail.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1498,137 +1498,137 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>NumberOfDependents</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER11</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.11.value</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'NumberOfDependents' → 'LOANPARAMETER15' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM2</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.1.value</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. A personal demographic and financial detail of the applicant.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER12</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.12.value</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Education' → 'LOANPARAMETER79' (frequency=2)</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM3</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.2.value</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the educational background of the applicant, a personal profile attribute.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>OtherEducation</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER13</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.13.value</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'OtherEducation' → 'LOANPARAMETER19' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM4</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.3.value</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Additional details on the applicant's education, a personal profile attribute.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1678,92 +1678,92 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>PassportNumber</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER14</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.14.value</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'PassportNumber' → 'LOANPARAMETER20' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM5</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.4.value</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. A unique Know Your Customer (KYC) identifier for the applicant.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>DrivingLicense</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER15</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.15.value</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'DrivingLicense' → 'LOANPARAMETER33' (frequency=2)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM6</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.5.value</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. A unique Know Your Customer (KYC) identifier for the applicant.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1813,47 +1813,47 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>RationCard</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER16</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.16.value</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'RationCard' → 'LOANPARAMETER23' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM7</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.6.value</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. A Know Your Customer (KYC) document detail for the applicant.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1960,30 +1960,30 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>LOANPARAMETER17</t>
+          <t>LOANPARAMETER10</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.17.value</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.10.value</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.9</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'CibilStatus' → 'LOANPARAMETER6' (frequency=3)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Represents the status of the bureau check process for the loan application, not a personal bureau attribute.</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2038,182 +2038,182 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>TVRGenerated</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER18</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.18.value</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'TVRGenerated' → 'LOANPARAMETER84' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER11</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.11.value</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A status flag indicating if a Telephonic Verification Report has been generated for the application.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>TVRStatus</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER19</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.19.value</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'TVRStatus' → 'LOANPARAMETER85' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER12</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.12.value</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Represents the outcome or status of the tele-verification process for the loan application.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>TVRRemark</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER20</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.20.value</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'TVRRemark' → 'LOANPARAMETER86' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER13</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.13.value</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Contains remarks from the application's tele-verification process.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>CibilResponse</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER21</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.21.value</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'CibilResponse' → 'LOANPARAMETER83' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER14</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.14.value</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Represents the bureau response data used for underwriting the loan application.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>LOANPARAMETER22</t>
+          <t>LOANAPPLICANTPARAM8</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.22.value</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.7.value</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'ReferenceName' → 'LOANPARAMETER69' (frequency=6)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The name of a personal reference provided by the applicant.</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2803,47 +2803,47 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>LeadFinancial</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER23</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.23.value</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Company Name' → 'LOANPARAMETER30' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM9</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.8.value</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The name of the applicant's employer, a core employment detail.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2865,25 +2865,25 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>LOANPARAMETER24</t>
+          <t>LOANAPPLICANTPARAM10</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.24.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.9.value</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'Nature Of Business' → 'LOANPARAMETER6' (frequency=24)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the applicant's industry or type of business, an employment profile detail.</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2938,47 +2938,47 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Job Profile</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>LeadFinancial</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>DOCUMENT</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER25</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.25.value</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Job Profile' → 'LOANPARAMETER31' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM11</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.10.value</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The applicant's designation or role at their job, an employment detail.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -3073,137 +3073,137 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>No Of Years Service</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>LeadFinancial</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER26</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.26.value</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'No Of Years Service' → 'LOANPARAMETER33' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM12</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.11.value</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the applicant's years of work experience, an employment profile attribute.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Per Month Salary</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>LeadFinancial</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER27</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.27.value</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Per Month Salary' → 'LOANPARAMETER34' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM13</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.12.value</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The applicant's monthly income, a key personal financial detail.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Mode Of Salary</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>LeadFinancial</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER28</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.28.value</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Mode Of Salary' → 'LOANPARAMETER35' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM14</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes how the applicant receives their salary, a personal financial detail.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -3225,757 +3225,757 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER29</t>
+          <t>LOANAPPLICANTPARAM15</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.29.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Appears to be a remark related to the applicant's financial or employment profile.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>SchemeName</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER15</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.15.value</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The name of the specific loan scheme or product being applied for.</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>SchemeID</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER16</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.16.value</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The unique identifier for the loan scheme, a core loan attribute.</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>CurrentMarketValue</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>VEHICLECURRENTMARKETVALUE</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.vehicleLoanDetails.currentMarketValue</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'CurrentMarketValue' in category 'LeadLoan' maps to 'VEHICLECURRENTMARKETVALUE'</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>OnRoadPrice</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER17</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.17.value</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The total price of the asset being financed, a key input for loan calculation.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>LoanAmount</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>PARTNERLOANAMOUNT</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.partnerLoanAmount</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'LoanAmount' in category 'LeadLoan' maps to 'PARTNERLOANAMOUNT'</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>MarginMoney</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER18</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.18.value</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The down payment or applicant's contribution towards the asset, a key loan financial parameter.</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>RateOfInt</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>INTERESTRATE</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.interestRate</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>alias_tier4</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Hybrid Remark' → 'LOANPARAMETER36' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Alias match (tier4): 'RateOfInt' → 'INTERESTRATE' (frequency=1)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>SchemeName</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Tenure</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER30</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.30.value</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SchemeName' → 'LOANPARAMETER55' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>SchemeID</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER31</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.31.value</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SchemeID' → 'LOANPARAMETER56' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>OnRoadPrice</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER32</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.32.value</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'OnRoadPrice' → 'LOANPARAMETER42' (frequency=2)</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>LoanAmount</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>LOAN</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>DISBURSEMENTAMOUNT</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.disbursementSchedules.0.disbursementAmount</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'LoanAmount' → 'DISBURSEMENTAMOUNT' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>MarginMoney</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER33</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.33.value</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'MarginMoney' → 'LOANPARAMETER57' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>RateOfInt</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>INTERESTRATE</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.interestRate</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'RateOfInt' → 'INTERESTRATE' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Tenure</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>tenure</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>loanAccount.tenure</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>TENUREINYEARS</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.tenureInYears</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Exact match: normalized 'Tenure' matches 'tenure'</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER34</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.34.value</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'IRR' → 'LOANPARAMETER58' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'Tenure' in category 'LeadLoan' maps to 'TENUREINYEARS'</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER19</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.19.value</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Internal Rate of Return, a core pricing and financial metric for the loan.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
           <t>EMI</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>APPLICANTPROPOSEDEMI</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>loanAccount.estimatedEmi</t>
         </is>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>alias_tier2</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Alias match (tier2): 'EMI' → 'APPLICANTPROPOSEDEMI' (frequency=17)</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="F71" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'EMI' in category 'LeadLoan' maps to 'APPLICANTPROPOSEDEMI'</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>ReduceEMIStatus</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER35</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.35.value</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'ReduceEMIStatus' → 'LOANPARAMETER62' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER20</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.20.value</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A status related to a loan feature (EMI reduction), which is a loan-level parameter.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>AddChargesStatus</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>FEE</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER36</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.36.value</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'AddChargesStatus' → 'LOANPARAMETER63' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER21</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.21.value</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A status related to adding charges to the loan, which is a loan-level parameter.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>AddLSIStatus</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER37</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.37.value</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'AddLSIStatus' → 'LOANPARAMETER64' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER22</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.22.value</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A status related to adding insurance (LSI) to the loan, a loan-level parameter.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>AddLsiLoanStatus</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>LOAN</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER38</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.38.value</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'AddLsiLoanStatus' → 'LOANPARAMETER65' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER23</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.23.value</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A status related to the insurance component of the loan, a loan-level parameter.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>LsiAmount</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER39</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.39.value</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'LsiAmount' → 'LOANPARAMETER66' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER24</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.24.value</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The amount of insurance financed as part of the loan, a loan-level financial component.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>TotalChargesAmount</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>LeadLoan</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>FEE</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER40</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.40.value</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'TotalChargesAmount' → 'LOANPARAMETER67' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>FinalLoanAmount</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>LOAN</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>TOTALLOANAMT</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.totalLoanAmount</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'FinalLoanAmount' → 'TOTALLOANAMT' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER25</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.25.value</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The total fees and charges associated with the loan, a core loan financial value.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FinalDisbursementAmount</t>
+          <t>FinalLoanAmount</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3985,17 +3985,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>NETDISBURSEMENTAMOUNT</t>
+          <t>TOTALLOANAMT</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.expectedDisbursementAmount</t>
+          <t>loanAccount.totalLoanAmount</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
@@ -4008,84 +4008,84 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
+          <t>Alias match (tier4): 'FinalLoanAmount' → 'TOTALLOANAMT' (frequency=1)</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>FinalDisbursementAmount</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>NETDISBURSEMENTAMOUNT</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.expectedDisbursementAmount</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>alias_tier4</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
           <t>Alias match (tier4): 'FinalDisbursementAmount' → 'NETDISBURSEMENTAMOUNT' (frequency=1)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>LTV</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER41</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.41.value</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>alias_tier3</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Alias match (tier3): 'LTV' → 'LOANPARAMETER30' (frequency=3)</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>VehicleType</t>
+          <t>LTV</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>LeadVehicle</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>VEHICLETYPE</t>
+          <t>LOANPARAMETER26</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.vehicleLoanDetails.vehicleType</t>
+          <t>loanAccount.loanParameters.26.value</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
@@ -4093,159 +4093,159 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Loan-to-Value is a fundamental derived metric for loan underwriting and structuring.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>VehicleType</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>LeadVehicle</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>VEHICLETYPE</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.vehicleLoanDetails.vehicleType</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>Exact match: normalized 'VehicleType' matches 'VEHICLETYPE'</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Make</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>LeadVehicle</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>VEHICLEMAKE</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>loanAccount.vehicleLoanDetails.make</t>
         </is>
       </c>
-      <c r="F81" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Make' → 'VEHICLEMAKE' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="F82" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'Make' in category 'LeadVehicle' maps to 'VEHICLEMAKE'</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>LeadVehicle</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>VEHICLEMODEL</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>loanAccount.vehicleLoanDetails.vehicleModel</t>
         </is>
       </c>
-      <c r="F82" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Model' → 'VEHICLEMODEL' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>SubModel</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>LeadVehicle</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER42</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.42.value</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SubModel' → 'LOANPARAMETER40' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F83" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'Model' in category 'LeadVehicle' maps to 'VEHICLEMODEL'</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>RegistrationNumber</t>
+          <t>SubModel</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>REGISTRATIONNUMBER</t>
+          <t>LOANPARAMETER27</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>customer.enterprise.registrationNumber</t>
+          <t>loanAccount.loanParameters.27.value</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
@@ -4273,249 +4273,249 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Specifies the model of the asset being financed, an asset-level detail tied to the loan.</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>RegistrationNumber</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>LeadVehicle</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>VEHICLEREGISTRATIONNUMBER</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.vehicleLoanDetails.registrationNumber</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>Exact match: normalized 'RegistrationNumber' matches 'REGISTRATIONNUMBER'</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>VehicleYear</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>LeadVehicle</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER43</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.43.value</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'VehicleYear' → 'LOANPARAMETER41' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'RegistrationNumber' in category 'LeadVehicle' maps to 'VEHICLEREGISTRATIONNUMBER'</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
+          <t>VehicleYear</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>LeadVehicle</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER28</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.28.value</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The manufacturing year of the vehicle asset, an asset-level detail tied to the loan.</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
           <t>DocumentID</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>LeadDocument</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>DOCUMENT</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>DOCUMENTID2</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>loanAccount.loanDocuments.1.documentId</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>document_id</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>Document ID detection: field contains document keyword and locator keyword (id)</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="F87" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'DocumentID' in category 'LeadDocument' maps to 'DOCUMENTID1'</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>LeadID</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>LeadDocument</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>DOCUMENT</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>APPLICATIONFILEID</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>loanAccount.applicationFileId</t>
         </is>
       </c>
-      <c r="F87" s="3" t="n">
+      <c r="F88" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>alias_tier4</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Alias match (tier4): 'LeadID' → 'APPLICATIONFILEID' (frequency=1)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>BankName</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>LeadBankDetails</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>CUSTOMERBANK</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.customerBankAccounts.0.customerBankName</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>alias_tier2</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>Alias match (tier2): 'BankName' → 'CUSTOMERBANK' (frequency=23)</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>IFSC</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>LeadBankDetails</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>IFSCCODE</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>customer.customerBankAccounts.0.ifscCode</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'IFSC' → 'IFSCCODE' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>OtherName</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>LeadDocument</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANTMOTHERNAME</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.motherName</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Category-aware exact override: 'OtherName' in category 'LeadDocument' maps to 'APPLICANTMOTHERNAME'</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>AccountNumber</t>
+          <t>BankName</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>CUSTOMERBANKACCOUNTNUMBER</t>
+          <t>CUSTOMERBANK</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>customer.customerBankAccounts.0.accountNumber</t>
+          <t>loanAccount.customer.customerBankAccounts.0.customerBankName</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'AccountNumber' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=23)</t>
+          <t>Alias match (tier2): 'BankName' → 'CUSTOMERBANK' (frequency=23)</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4558,59 +4558,59 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>IFSC</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>LeadBankDetails</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANTPARTNERBRANCHNAME</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>loanAccount.loanAccountAdditional.partnerBranchName</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>alias_tier2</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>Alias match (tier2): 'Branch' → 'APPLICANTPARTNERBRANCHNAME' (frequency=14)</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>IFSCCODE</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>customer.customerBankAccounts.0.ifscCode</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>alias_tier4</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Alias match (tier4): 'IFSC' → 'IFSCCODE' (frequency=1)</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>AddressType</t>
+          <t>AccountNumber</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadBankDetails</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4620,25 +4620,25 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>ADDRESSPROOFTYPE</t>
+          <t>CUSTOMERBANKACCOUNTNUMBER</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>customer.addressProof</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>0.8148</v>
+          <t>customer.customerBankAccounts.0.accountNumber</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.92</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Fuzzy: 'AddressType' ~ 'ADDRESSPROOFTYPE' score=0.81</t>
+          <t>Alias match (tier2): 'AccountNumber' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=23)</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4650,12 +4650,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>PanchardNumber</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadBankDetails</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4665,25 +4665,25 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>PANNUMBER</t>
+          <t>APPLICANTPARTNERBRANCHNAME</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>customer.panNo</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>0.8144</v>
+          <t>loanAccount.loanAccountAdditional.partnerBranchName</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0.92</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Embedding: 'PanchardNumber' → 'PANNUMBER' sim=0.814</t>
+          <t>Alias match (tier2): 'Branch' → 'APPLICANTPARTNERBRANCHNAME' (frequency=14)</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -4695,166 +4695,166 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>LoanTypeName</t>
+          <t>AddressType</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>ADDRESSPROOFTYPE</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>customer.addressProof</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>fuzzy</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Fuzzy: 'AddressType' ~ 'ADDRESSPROOFTYPE' score=0.81</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>PanchardNumber</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>LeadProfile</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>PANNUMBER</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>customer.panNo</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>0.8144</v>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Embedding: 'PanchardNumber' → 'PANNUMBER' sim=0.814</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>TenureType</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>LeadLoan</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
           <t>LOAN</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANTLOANTYPE</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>loanAccount.loanType</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>llm_semantic</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>The field 'LoanTypeName' directly refers to the type of the loan, which matches the business concept of 'APPLICANTLOANTYPE'.</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>AddressOR</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM1</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.0.value</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>The field 'AddressOR' is an applicant-related address field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Remark</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM2</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.1.value</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>The field 'Remark' is a generic applicant-related field with no specific match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>tenure</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.tenure</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>0.8362000000000001</v>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Embedding: 'TenureType' → 'tenure' sim=0.836</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>LoanTypeName</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>LeadReference</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>BUSINESSVERIFICATIONADDRESS</t>
+          <t>APPLICANTLOANTYPE</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.customer.verifications.0.address</t>
+          <t>loanAccount.loanType</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>The field 'Address' in the 'LeadReference' category maps to the address of a reference, which corresponds to 'BUSINESSVERIFICATIONADDRESS'.</t>
+          <t>The field 'LoanTypeName' semantically corresponds to 'APPLICANTLOANTYPE' which represents the type of loan.</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -4875,31 +4875,31 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Relation</t>
+          <t>ExShowroomPrice</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>LeadReference</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>BUSINESSVERIFICATIONENTERPRISERELATION1TYPE</t>
+          <t>VEHICLEPRICE</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.customer.verifications.0.relationship</t>
+          <t>loanAccount.vehicleLoanDetails.price</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>The field 'Relation' in the 'LeadReference' category maps to the relationship of a reference, which corresponds to 'BUSINESSVERIFICATIONENTERPRISERELATION1TYPE'.</t>
+          <t>The field 'ExShowroomPrice' is a specific price for a vehicle, which directly maps to VEHICLEPRICE.</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -4920,7 +4920,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AddressID</t>
+          <t>AddressOR</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM3</t>
+          <t>LOANAPPLICANTPARAM16</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.2.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>The field 'AddressID' is an applicant-related field with no direct match in the available keys.</t>
+          <t>The field 'AddressOR' is a custom address field with no direct mapping available.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4963,149 +4963,149 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>RelationOther</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>LeadContact</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANTPERSONALDISCUSSIONCOMMENTS</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.personalDiscussionComments</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>The field 'Remark' is a general comments field which best maps to 'APPLICANTPERSONALDISCUSSIONCOMMENTS'.</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>LeadReference</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM4</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.3.value</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>The field 'RelationOther' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>CurrentMarketValue</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM5</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.4.value</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>The field 'CurrentMarketValue' is an applicant-related financial field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>BUSINESSVERIFICATIONADDRESS</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.verifications.0.address</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>The field 'Address' with category 'LeadReference' corresponds to the address of a verification reference.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>TenureType</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM6</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.5.value</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>The field 'TenureType' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Relation</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>LeadReference</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>BUSINESSVERIFICATIONENTERPRISERELATION1TYPE</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.verifications.0.relationship</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>The field 'Relation' with category 'LeadReference' corresponds to the relationship of a verification reference.</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>AddressID</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>LeadFinancial</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM7</t>
+          <t>LOANAPPLICANTPARAM17</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.6.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>The field 'Type' from 'LeadFinancial' is a generic applicant-related field with no specific match in the available keys.</t>
+          <t>The field 'AddressID' is a custom identifier for an address with no direct mapping.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>TypeName</t>
+          <t>RelationOther</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadReference</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -5160,16 +5160,16 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>APPLICANTBORROWERTYPE</t>
+          <t>BUSINESSVERIFICATIONCOMMENTS</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerType</t>
-        </is>
-      </c>
-      <c r="F104" s="6" t="n">
-        <v>0.88</v>
+          <t>loanAccount.customer.verifications.0.remarks</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.9</v>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>'TypeName' in the 'LeadProfile' category likely refers to the type of the applicant, which matches 'APPLICANTBORROWERTYPE'.</t>
+          <t>The field 'RelationOther' for custom relationship text can be stored in the verification comments field.</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -5190,12 +5190,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FatherSpouse</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadFinancial</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM8</t>
+          <t>LOANAPPLICANTPARAM18</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.7.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>The field 'FatherSpouse' is an applicant-related field that combines two concepts and has no direct match.</t>
+          <t>The field 'Type' is too generic and its category 'LeadFinancial' does not provide enough context for a specific mapping.</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5233,144 +5233,144 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>TypeName</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>LeadProfile</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERTYPE</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.customerType</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>The field 'TypeName' in the 'LeadProfile' category strongly suggests it is the applicant's customer type.</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>FatherSpouse</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>LeadProfile</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANTFATHERNAME</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.fatherFirstName</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>The field 'FatherSpouse' likely contains either the father or spouse name and is mapped to the more common 'APPLICANTFATHERNAME'.</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>CibilGenerated</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>LeadProfile</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM9</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.8.value</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="n">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM19</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>llm_loanapplicantparam</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>The field 'CibilGenerated' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>The field 'CibilGenerated' appears to be a flag with no corresponding key in the system.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>IsPrimaryText</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM10</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.9.value</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>The field 'IsPrimaryText' is an applicant-related address field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>NoOfYearResiding</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANTINCURRENTADDRESSSINCE</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.inCurrentAddressSince</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>llm_semantic</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>'NoOfYearResiding' is semantically equivalent to the information captured by 'APPLICANTINCURRENTADDRESSSINCE'.</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>AreaOther</t>
+          <t>IsPrimaryText</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM11</t>
+          <t>LOANAPPLICANTPARAM20</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.10.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.19.value</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>The field 'AreaOther' is an applicant-related address field with no direct match in the available keys.</t>
+          <t>The field 'IsPrimaryText' appears to be a flag for a primary address with no corresponding key in the system.</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5413,104 +5413,104 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>AreaPanchayatPopulation</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>NoOfYearResiding</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>LeadAddress</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM12</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.11.value</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>The field 'AreaPanchayatPopulation' is a specific applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANTINCURRENTADDRESSSINCE</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.inCurrentAddressSince</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>The field 'NoOfYearResiding' captures the duration at an address which semantically matches 'APPLICANTINCURRENTADDRESSSINCE'.</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>IsPrimary</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM13</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.12.value</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>The field 'IsPrimary' is an applicant-related contact field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>AreaOther</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>LeadAddress</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>ADDRESSREMARKS</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.customerAdditional.addressRemarks</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>The field 'AreaOther' for other area text can be stored in the address remarks field.</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ContactType</t>
+          <t>AreaPanchayatPopulation</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>LeadContact</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM14</t>
+          <t>LOANAPPLICANTPARAM21</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.20.value</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>The field 'ContactType' is an applicant-related field with no direct match in the available keys.</t>
+          <t>The field 'AreaPanchayatPopulation' is a specific demographic data point with no corresponding key.</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>IsPrimary</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM15</t>
+          <t>LOANAPPLICANTPARAM22</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.21.value</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>The field 'Value' is a generic applicant-related field with no specific match in the available keys.</t>
+          <t>The field 'IsPrimary' appears to be a flag for a primary contact with no corresponding key in the system.</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>ContactType</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM16</t>
+          <t>LOANAPPLICANTPARAM23</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.22.value</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>The field 'Extension' for a contact number is an applicant-related field with no direct match.</t>
+          <t>The field 'ContactType' has no corresponding key as the system uses specific fields for different contact types.</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5638,59 +5638,59 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>ReferenceID</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>LeadReference</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM17</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>The field 'ReferenceID' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>LeadContact</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERMOBILENO</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.mobilePhone</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>The field 'Value' in the 'LeadContact' category most likely represents the applicant's mobile number.</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ExShowroomPrice</t>
+          <t>Extension</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>LeadLoan</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM18</t>
+          <t>LOANAPPLICANTPARAM24</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.23.value</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>The field 'ExShowroomPrice' is an applicant-related financial field with no direct match in the available keys.</t>
+          <t>The field 'Extension' for a phone number extension has no corresponding key in the system.</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -5728,47 +5728,47 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>OtherName</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>LeadDocument</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>DOCUMENTNAME3</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>loanAccount.loanDocuments.2.document</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>llm_pattern_document_name</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>The field 'OtherName' in the 'LeadDocument' category indicates the name of a document.</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ReferenceID</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>LeadReference</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM25</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>The field 'ReferenceID' is a custom identifier for a reference with no direct mapping.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5790,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM19</t>
+          <t>LOANAPPLICANTPARAM26</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.25.value</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>The field 'Details' is a generic applicant-related field with no specific match in the available keys.</t>
+          <t>The field 'Details' under 'LeadBankDetails' is too generic to be mapped to a specific bank detail field.</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME4</t>
+          <t>DOCUMENTNAME3</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.3.document</t>
+          <t>loanAccount.loanDocuments.2.document</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>The field 'DocumentType' refers to the type or name of the document.</t>
+          <t>The field DocumentType clearly refers to the name or type of a document.</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME5</t>
+          <t>DOCUMENTNAME4</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.4.document</t>
+          <t>loanAccount.loanDocuments.3.document</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>The field 'FileName' refers to the name of the document file.</t>
+          <t>The field FileName clearly refers to the name of a document file.</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTID6</t>
+          <t>DOCUMENTID5</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.5.documentId</t>
+          <t>loanAccount.loanDocuments.4.documentId</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>The field 'FilePath' serves as a locator for the document, which is conceptually equivalent to a document ID.</t>
+          <t>The field FilePath clearly refers to the location or identifier of a document.</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -5964,7 +5964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>akmeee</t>
+          <t>AKMEEE</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-06 15:30:53</t>
+          <t>2026-04-07 11:22:56</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -6083,13 +6083,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>document_name</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -6099,51 +6099,51 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>document_name</t>
+          <t>embedding</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>fuzzy</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>llm_loanapplicantparam</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26">
@@ -6200,50 +6200,52 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Fields Needing Review:</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Fields Needing Review:</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>72</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fields:</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Fields:</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LeadID</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>LeadID</t>
+          <t>LeadCode</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6255,7 +6257,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>LeadCode</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6267,7 +6269,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>LeadStage</t>
+          <t>CibilType</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6279,7 +6281,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>SalesPointName</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6291,7 +6293,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>ReferredBy</t>
+          <t>StateName</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6303,7 +6305,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>SubProduct</t>
+          <t>CityName</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6315,7 +6317,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>SubProductCategory</t>
+          <t>DistrictName</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6327,7 +6329,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>CreateDate</t>
+          <t>Company Address</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6339,19 +6341,19 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>RegisterThrough</t>
+          <t>Hybrid Remark</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.70</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>RateOfInt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6363,7 +6365,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>NumberOfDependents</t>
+          <t>FinalLoanAmount</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6375,7 +6377,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>FinalDisbursementAmount</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6387,7 +6389,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>OtherEducation</t>
+          <t>LeadID</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6399,7 +6401,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>PassportNumber</t>
+          <t>IFSC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6411,136 +6413,124 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>DrivingLicense</t>
+          <t>AddressOR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>RationCard</t>
+          <t>AddressID</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>CibilType</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="C49" t="inlineStr">
         <is>
-          <t>TVRGenerated</t>
+          <t>CibilGenerated</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="C50" t="inlineStr">
         <is>
-          <t>TVRStatus</t>
+          <t>IsPrimaryText</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="C51" t="inlineStr">
         <is>
-          <t>TVRRemark</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>... and 52 more</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+          <t>... and 6 more</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>Mandatory Fields Missing:</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B53" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Confidence Distribution:</t>
+        </is>
+      </c>
+    </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Confidence Distribution:</t>
-        </is>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0.90-1.00</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>0.90-1.00</t>
+          <t>0.80-0.89</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>0.80-0.89</t>
+          <t>0.70-0.79</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>0.70-0.79</t>
+          <t>0.00-0.69</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>0.00-0.69</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6555,7 +6545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6629,7 +6619,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -6709,12 +6699,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LeadStage</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadProfile</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6724,12 +6714,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER1</t>
+          <t>APPLICANTCUSTOMERTITLE</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.1.value</t>
+          <t>loanAccount.customer.title</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
@@ -6742,7 +6732,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'LeadStage' → 'LOANPARAMETER0' (frequency=1)</t>
+          <t>Alias match (tier4): 'Title' → 'APPLICANTCUSTOMERTITLE' (frequency=2)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6754,12 +6744,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SalesPointName</t>
+          <t>CibilType</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadProfile</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6769,12 +6759,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER4</t>
+          <t>NAMEOFBUREAU</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.4.value</t>
+          <t>customer.cbRemarks</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -6787,7 +6777,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'SalesPointName' → 'LOANPARAMETER2' (frequency=1)</t>
+          <t>Alias match (tier4): 'CibilType' → 'NAMEOFBUREAU' (frequency=1)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6799,12 +6789,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ReferredBy</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -6814,12 +6804,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER5</t>
+          <t>ADDRESSREMARKS</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.5.value</t>
+          <t>loanAccount.customer.customerAdditional.addressRemarks</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
@@ -6832,7 +6822,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'ReferredBy' → 'LOANPARAMETER3' (frequency=1)</t>
+          <t>Alias match (tier4): 'Area' → 'ADDRESSREMARKS' (frequency=1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6844,12 +6834,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SubProduct</t>
+          <t>StateName</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -6859,12 +6849,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER6</t>
+          <t>APPLICANTSTATE</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.6.value</t>
+          <t>loanAccount.customer.state</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
@@ -6877,7 +6867,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'SubProduct' → 'LOANPARAMETER43' (frequency=1)</t>
+          <t>Alias match (tier4): 'StateName' → 'APPLICANTSTATE' (frequency=1)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6889,12 +6879,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SubProductCategory</t>
+          <t>CityName</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -6904,12 +6894,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER7</t>
+          <t>VILLAGEORCITY</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.7.value</t>
+          <t>customer.villageName</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
@@ -6922,7 +6912,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'SubProductCategory' → 'LOANPARAMETER44' (frequency=1)</t>
+          <t>Alias match (tier4): 'CityName' → 'VILLAGEORCITY' (frequency=1)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6934,12 +6924,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CreateDate</t>
+          <t>DistrictName</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -6949,12 +6939,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER8</t>
+          <t>DISTRICT</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.8.value</t>
+          <t>customer.district</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
@@ -6967,7 +6957,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'CreateDate' → 'LOANPARAMETER116' (frequency=1)</t>
+          <t>Alias match (tier4): 'DistrictName' → 'DISTRICT' (frequency=1)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -6979,12 +6969,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RegisterThrough</t>
+          <t>Company Address</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadFinancial</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6994,12 +6984,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER9</t>
+          <t>APPLICANTCOMMADDRESSSTREET</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.9.value</t>
+          <t>loanAccount.customer.mailingStreet</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
@@ -7012,7 +7002,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'RegisterThrough' → 'LOANPARAMETER125' (frequency=1)</t>
+          <t>Alias match (tier4): 'Company Address' → 'APPLICANTCOMMADDRESSSTREET' (frequency=1)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7024,12 +7014,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Hybrid Remark</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadFinancial</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7039,25 +7029,25 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERTITLE</t>
+          <t>LOANAPPLICANTPARAM15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.title</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'Title' → 'APPLICANTCUSTOMERTITLE' (frequency=2)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Appears to be a remark related to the applicant's financial or employment profile.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7069,27 +7059,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NumberOfDependents</t>
+          <t>RateOfInt</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER11</t>
+          <t>INTERESTRATE</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.11.value</t>
+          <t>loanAccount.interestRate</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
@@ -7102,7 +7092,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'NumberOfDependents' → 'LOANPARAMETER15' (frequency=1)</t>
+          <t>Alias match (tier4): 'RateOfInt' → 'INTERESTRATE' (frequency=1)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7114,27 +7104,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>FinalLoanAmount</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER12</t>
+          <t>TOTALLOANAMT</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.12.value</t>
+          <t>loanAccount.totalLoanAmount</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
@@ -7147,7 +7137,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'Education' → 'LOANPARAMETER79' (frequency=2)</t>
+          <t>Alias match (tier4): 'FinalLoanAmount' → 'TOTALLOANAMT' (frequency=1)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7159,27 +7149,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OtherEducation</t>
+          <t>FinalDisbursementAmount</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER13</t>
+          <t>NETDISBURSEMENTAMOUNT</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.13.value</t>
+          <t>loanAccount.expectedDisbursementAmount</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
@@ -7192,7 +7182,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'OtherEducation' → 'LOANPARAMETER19' (frequency=1)</t>
+          <t>Alias match (tier4): 'FinalDisbursementAmount' → 'NETDISBURSEMENTAMOUNT' (frequency=1)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7204,27 +7194,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PassportNumber</t>
+          <t>LeadID</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadDocument</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER14</t>
+          <t>APPLICATIONFILEID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.14.value</t>
+          <t>loanAccount.applicationFileId</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
@@ -7237,7 +7227,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'PassportNumber' → 'LOANPARAMETER20' (frequency=1)</t>
+          <t>Alias match (tier4): 'LeadID' → 'APPLICATIONFILEID' (frequency=1)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -7249,12 +7239,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DrivingLicense</t>
+          <t>IFSC</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadBankDetails</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7264,12 +7254,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER15</t>
+          <t>IFSCCODE</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.15.value</t>
+          <t>customer.customerBankAccounts.0.ifscCode</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -7282,7 +7272,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'DrivingLicense' → 'LOANPARAMETER33' (frequency=2)</t>
+          <t>Alias match (tier4): 'IFSC' → 'IFSCCODE' (frequency=1)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7294,12 +7284,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RationCard</t>
+          <t>AddressOR</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7309,25 +7299,25 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER16</t>
+          <t>LOANAPPLICANTPARAM16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.16.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'RationCard' → 'LOANPARAMETER23' (frequency=1)</t>
+          <t>The field 'AddressOR' is a custom address field with no direct mapping available.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7339,12 +7329,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CibilType</t>
+          <t>AddressID</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7354,25 +7344,25 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>NAMEOFBUREAU</t>
+          <t>LOANAPPLICANTPARAM17</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>customer.cbRemarks</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'CibilType' → 'NAMEOFBUREAU' (frequency=1)</t>
+          <t>The field 'AddressID' is a custom identifier for an address with no direct mapping.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7384,12 +7374,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TVRGenerated</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadFinancial</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7399,25 +7389,25 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER18</t>
+          <t>LOANAPPLICANTPARAM18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.18.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'TVRGenerated' → 'LOANPARAMETER84' (frequency=1)</t>
+          <t>The field 'Type' is too generic and its category 'LeadFinancial' does not provide enough context for a specific mapping.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -7429,7 +7419,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TVRStatus</t>
+          <t>CibilGenerated</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -7444,25 +7434,25 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER19</t>
+          <t>LOANAPPLICANTPARAM19</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.19.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'TVRStatus' → 'LOANPARAMETER85' (frequency=1)</t>
+          <t>The field 'CibilGenerated' appears to be a flag with no corresponding key in the system.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7474,12 +7464,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TVRRemark</t>
+          <t>IsPrimaryText</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -7489,25 +7479,25 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER20</t>
+          <t>LOANAPPLICANTPARAM20</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.20.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.19.value</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'TVRRemark' → 'LOANPARAMETER86' (frequency=1)</t>
+          <t>The field 'IsPrimaryText' appears to be a flag for a primary address with no corresponding key in the system.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -7519,12 +7509,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CibilResponse</t>
+          <t>AreaPanchayatPopulation</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -7534,25 +7524,25 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER21</t>
+          <t>LOANAPPLICANTPARAM21</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.21.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.20.value</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'CibilResponse' → 'LOANPARAMETER83' (frequency=1)</t>
+          <t>The field 'AreaPanchayatPopulation' is a specific demographic data point with no corresponding key.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7564,12 +7554,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>IsPrimary</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -7579,25 +7569,25 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ADDRESSREMARKS</t>
+          <t>LOANAPPLICANTPARAM22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.addressRemarks</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.21.value</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'Area' → 'ADDRESSREMARKS' (frequency=1)</t>
+          <t>The field 'IsPrimary' appears to be a flag for a primary contact with no corresponding key in the system.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -7609,12 +7599,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>StateName</t>
+          <t>ContactType</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -7624,25 +7614,25 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTSTATE</t>
+          <t>LOANAPPLICANTPARAM23</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.state</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.22.value</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'StateName' → 'APPLICANTSTATE' (frequency=1)</t>
+          <t>The field 'ContactType' has no corresponding key as the system uses specific fields for different contact types.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -7654,12 +7644,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CityName</t>
+          <t>Extension</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -7669,25 +7659,25 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>VILLAGEORCITY</t>
+          <t>LOANAPPLICANTPARAM24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>customer.villageName</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.23.value</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'CityName' → 'VILLAGEORCITY' (frequency=1)</t>
+          <t>The field 'Extension' for a phone number extension has no corresponding key in the system.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -7699,12 +7689,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DistrictName</t>
+          <t>ReferenceID</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadReference</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -7714,25 +7704,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DISTRICT</t>
+          <t>LOANAPPLICANTPARAM25</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>customer.district</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'DistrictName' → 'DISTRICT' (frequency=1)</t>
+          <t>The field 'ReferenceID' is a custom identifier for a reference with no direct mapping.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7744,12 +7734,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Company Name</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LeadFinancial</t>
+          <t>LeadBankDetails</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -7759,25 +7749,25 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER23</t>
+          <t>LOANAPPLICANTPARAM26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.23.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.25.value</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>alias_tier4</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'Company Name' → 'LOANPARAMETER30' (frequency=1)</t>
+          <t>The field 'Details' under 'LeadBankDetails' is too generic to be mapped to a specific bank detail field.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -7786,2078 +7776,8 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Job Profile</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>LeadFinancial</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>DOCUMENT</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER25</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.25.value</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Job Profile' → 'LOANPARAMETER31' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Company Address</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>LeadFinancial</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANTCOMMADDRESSSTREET</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.mailingStreet</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Company Address' → 'APPLICANTCOMMADDRESSSTREET' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>No Of Years Service</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>LeadFinancial</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER26</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.26.value</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'No Of Years Service' → 'LOANPARAMETER33' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Per Month Salary</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>LeadFinancial</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER27</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.27.value</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Per Month Salary' → 'LOANPARAMETER34' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Mode Of Salary</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>LeadFinancial</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER28</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.28.value</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Mode Of Salary' → 'LOANPARAMETER35' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Hybrid Remark</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>LeadFinancial</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER29</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.29.value</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Hybrid Remark' → 'LOANPARAMETER36' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SchemeName</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER30</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.30.value</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SchemeName' → 'LOANPARAMETER55' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SchemeID</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER31</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.31.value</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SchemeID' → 'LOANPARAMETER56' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>OnRoadPrice</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER32</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.32.value</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'OnRoadPrice' → 'LOANPARAMETER42' (frequency=2)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>LoanAmount</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>DISBURSEMENTAMOUNT</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.disbursementSchedules.0.disbursementAmount</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'LoanAmount' → 'DISBURSEMENTAMOUNT' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>MarginMoney</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER33</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.33.value</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'MarginMoney' → 'LOANPARAMETER57' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>RateOfInt</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>INTERESTRATE</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.interestRate</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'RateOfInt' → 'INTERESTRATE' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER34</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.34.value</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'IRR' → 'LOANPARAMETER58' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ReduceEMIStatus</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER35</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.35.value</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'ReduceEMIStatus' → 'LOANPARAMETER62' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>AddChargesStatus</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>FEE</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER36</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.36.value</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'AddChargesStatus' → 'LOANPARAMETER63' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>AddLSIStatus</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER37</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.37.value</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'AddLSIStatus' → 'LOANPARAMETER64' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>AddLsiLoanStatus</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER38</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.38.value</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'AddLsiLoanStatus' → 'LOANPARAMETER65' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>LsiAmount</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER39</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.39.value</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'LsiAmount' → 'LOANPARAMETER66' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TotalChargesAmount</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>FEE</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER40</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.40.value</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'TotalChargesAmount' → 'LOANPARAMETER67' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>FinalLoanAmount</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>TOTALLOANAMT</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.totalLoanAmount</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'FinalLoanAmount' → 'TOTALLOANAMT' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>FinalDisbursementAmount</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>NETDISBURSEMENTAMOUNT</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.expectedDisbursementAmount</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'FinalDisbursementAmount' → 'NETDISBURSEMENTAMOUNT' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>LeadVehicle</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>VEHICLEMAKE</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.vehicleLoanDetails.make</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Make' → 'VEHICLEMAKE' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>LeadVehicle</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>VEHICLEMODEL</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.vehicleLoanDetails.vehicleModel</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'Model' → 'VEHICLEMODEL' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>SubModel</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>LeadVehicle</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER42</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.42.value</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'SubModel' → 'LOANPARAMETER40' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>VehicleYear</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>LeadVehicle</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER43</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.43.value</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'VehicleYear' → 'LOANPARAMETER41' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>LeadID</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>LeadDocument</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>APPLICATIONFILEID</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.applicationFileId</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'LeadID' → 'APPLICATIONFILEID' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>IFSC</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>LeadBankDetails</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>IFSCCODE</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>customer.customerBankAccounts.0.ifscCode</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'IFSC' → 'IFSCCODE' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>AddressOR</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM1</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.0.value</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>The field 'AddressOR' is an applicant-related address field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Remark</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM2</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.1.value</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>The field 'Remark' is a generic applicant-related field with no specific match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>AddressID</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM3</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.2.value</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>The field 'AddressID' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>RelationOther</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>LeadReference</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM4</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.3.value</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>The field 'RelationOther' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CurrentMarketValue</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM5</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.4.value</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>The field 'CurrentMarketValue' is an applicant-related financial field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TenureType</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM6</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.5.value</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>The field 'TenureType' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>LeadFinancial</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM7</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.6.value</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>The field 'Type' from 'LeadFinancial' is a generic applicant-related field with no specific match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>FatherSpouse</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>LeadProfile</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM8</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.7.value</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>The field 'FatherSpouse' is an applicant-related field that combines two concepts and has no direct match.</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CibilGenerated</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>LeadProfile</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM9</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.8.value</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>The field 'CibilGenerated' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>IsPrimaryText</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM10</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.9.value</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>The field 'IsPrimaryText' is an applicant-related address field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>AreaOther</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM11</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.10.value</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>The field 'AreaOther' is an applicant-related address field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>AreaPanchayatPopulation</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>LeadAddress</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM12</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.11.value</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>The field 'AreaPanchayatPopulation' is a specific applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>IsPrimary</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM13</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.12.value</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>The field 'IsPrimary' is an applicant-related contact field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>ContactType</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM14</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>The field 'ContactType' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM15</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>The field 'Value' is a generic applicant-related field with no specific match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Extension</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM16</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>The field 'Extension' for a contact number is an applicant-related field with no direct match.</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>ReferenceID</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>LeadReference</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM17</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>The field 'ReferenceID' is an applicant-related field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>ExShowroomPrice</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM18</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>The field 'ExShowroomPrice' is an applicant-related financial field with no direct match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>LeadBankDetails</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM19</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>The field 'Details' is a generic applicant-related field with no specific match in the available keys.</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I73"/>
+  <autoFilter ref="A1:I27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>